--- a/output/pdf_financials_xlsx/MRG.UN.xlsx
+++ b/output/pdf_financials_xlsx/MRG.UN.xlsx
@@ -2211,46 +2211,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.822</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>32.553</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>8.599</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.587</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>25.121</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>16.786</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>17.748</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>26.562</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>14.636</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>17.825</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>51.258</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>114.634</v>
       </c>
     </row>
     <row r="35">
@@ -2309,46 +2309,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.822</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>32.553</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>8.599</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.587</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>25.121</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>16.786</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>17.748</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>26.562</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>14.636</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>17.825</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>51.258</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>114.634</v>
       </c>
     </row>
     <row r="37">
@@ -2897,46 +2897,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.226</v>
+        <v>1.316</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>95.38200000000001</v>
+        <v>90.56</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>14.237</v>
+        <v>8.987</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>43.941</v>
+        <v>11.388</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>54.241</v>
+        <v>45.642</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>57.838</v>
+        <v>50.251</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>38.672</v>
+        <v>13.551</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>34.123</v>
+        <v>17.337</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>50.916</v>
+        <v>33.168</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>113.565</v>
+        <v>87.003</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>190.7</v>
+        <v>176.064</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>33.597</v>
+        <v>15.772</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>155.098</v>
+        <v>103.84</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>140.472</v>
+        <v>25.838</v>
       </c>
     </row>
     <row r="49">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -27100,7 +27100,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -31880,7 +31880,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -37842,7 +37842,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -39934,7 +39934,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E395" s="5" t="n">
@@ -42388,7 +42388,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E424" s="5" t="n">
